--- a/artfynd/A 33930-2025 artfynd.xlsx
+++ b/artfynd/A 33930-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654405</v>
+        <v>121654401</v>
       </c>
       <c r="B2" t="n">
-        <v>97094</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329586</v>
+        <v>329618</v>
       </c>
       <c r="R2" t="n">
-        <v>6552960</v>
+        <v>6552997</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 kvadrat</t>
+          <t>5 kvadratmeter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654508</v>
+        <v>121654403</v>
       </c>
       <c r="B3" t="n">
-        <v>97094</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329635</v>
+        <v>329601</v>
       </c>
       <c r="R3" t="n">
-        <v>6553046</v>
+        <v>6552970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket rikligt. Ca 100m2</t>
+          <t>20 kvadrat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654401</v>
+        <v>121654405</v>
       </c>
       <c r="B4" t="n">
-        <v>97094</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329618</v>
+        <v>329586</v>
       </c>
       <c r="R4" t="n">
-        <v>6552997</v>
+        <v>6552960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5 kvadratmeter</t>
+          <t>3 kvadrat</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654403</v>
+        <v>121654508</v>
       </c>
       <c r="B5" t="n">
-        <v>97094</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329601</v>
+        <v>329635</v>
       </c>
       <c r="R5" t="n">
-        <v>6552970</v>
+        <v>6553046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20 kvadrat</t>
+          <t>Mycket rikligt. Ca 100m2</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 33930-2025 artfynd.xlsx
+++ b/artfynd/A 33930-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654405</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>